--- a/Result/profitability/2731.xlsx
+++ b/Result/profitability/2731.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8050,6 +8050,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8331</v>
+      </c>
+      <c r="D61" t="n">
+        <v>7139</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1193</v>
+      </c>
+      <c r="F61" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="G61" t="n">
+        <v>316</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>60</v>
+      </c>
+      <c r="J61" t="n">
+        <v>375</v>
+      </c>
+      <c r="K61" t="n">
+        <v>290</v>
+      </c>
+      <c r="L61" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.49125</v>
+      </c>
+      <c r="N61" t="n">
+        <v>15.28375</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="X61" t="n">
+        <v>-0.2541966426858513</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-1.629999999999999</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-0.1021943573667711</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-0.8300000000000001</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>-0.2106598984771574</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>-0.0843989769820972</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK61" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
